--- a/plantillas/Plantilla_Marco_Conceptual.xlsx
+++ b/plantillas/Plantilla_Marco_Conceptual.xlsx
@@ -1,58 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="CONCEPTOS" sheetId="1" r:id="rId1"/>
+    <sheet name="LEEME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CONCEPTOS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A2E"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A2E"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A2E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="002C5F6F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A2E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A2E"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9F4ED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +87,105 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="001E2A2E"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +264,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +298,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +332,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,119 +467,434 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>MARCO CONCEPTUAL — Conceptos metodológicos</v>
-      </c>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Marco Conceptual del grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Un concepto por fila. mostrar_en_web: TRUE.</v>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>id</v>
-      </c>
-      <c r="B3" t="str">
-        <v>orden</v>
-      </c>
-      <c r="C3" t="str">
-        <v>icono</v>
-      </c>
-      <c r="D3" t="str">
-        <v>titulo</v>
-      </c>
-      <c r="E3" t="str">
-        <v>formula</v>
-      </c>
-      <c r="F3" t="str">
-        <v>descripcion</v>
-      </c>
-      <c r="G3" t="str">
-        <v>mostrar_en_web</v>
-      </c>
-      <c r="H3" t="str">
-        <v>estado</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Para qué sirve</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Son los conceptos con los que trabaja el grupo: el vocabulario común. Cada concepto se muestra como una tarjeta en el sitio.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>directorio-colaborativo</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Dónde se ve</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sitio → Recursos del grupo → tarjeta «Marco conceptual».</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se usa</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Escribí un concepto por fila en la pestaña CONCEPTOS. Vienen 6 ejemplos ya cargados: editalos, borrá los que no usen y agregá los suyos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Qué va en cada columna</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>OBLIGATORIO. El nombre del concepto. Ej: «Devolución». Es lo que se ve más grande en la tarjeta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>OBLIGATORIO. Qué significa, en dos o tres líneas y en criollo. Es el texto de la tarjeta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>icono</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Opcional. Un emoji para la tarjeta. Si lo dejás vacío se usa 📌. Se copian de cualquier lado (🏛️ 📋 🔄 🎯 📊 🤝).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>frase_corta</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Opcional. Una frase de tres o cuatro palabras que resume el concepto; aparece en gris chiquito abajo del título. Si no se te ocurre ninguna, dejala vacía: la tarjeta se ve igual de bien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>mostrar_en_web</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Escribí TRUE para que se vea, FALSE para esconderlo sin borrar la fila. Si lo dejás vacío, se muestra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>orden</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Opcional. El número define en qué orden aparecen las tarjetas. Si está vacío, se usan en el orden de la planilla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Cómo conectarla</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Subí este archivo a la carpeta del grupo en Drive, compartilo como Lector con la cuenta de servicio del sitio, y pegá su link en Configuración → Marco Conceptual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Ojo</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>No cambies los nombres de las columnas de la fila 3 de CONCEPTOS: el sitio las busca por ese nombre.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>CONCEPTOS — el vocabulario común del grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Un concepto por fila. Las 6 filas de abajo son ejemplos reales: editalos, borrá los que no correspondan y sumá los del grupo. Solo «titulo» y «descripcion» son obligatorios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>icono</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>frase_corta</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>mostrar_en_web</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Colaborativo</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Un espacio de dirección donde cada empresa presenta sus decisiones y recibe la mirada de otros empresarios. No es una consultoría: son pares que aportan desde su propia experiencia.</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>🏛️</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>entre pares, no consultores</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="str">
-        <v>🏛️</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Directorio Colaborativo</v>
-      </c>
-      <c r="E4" t="str">
-        <v>empresa × grupo = aprendizaje</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Descripción…</v>
-      </c>
-      <c r="G4" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Proceso Estratégico</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>La presentación que hace una empresa sobre un desafío concreto para recibir devoluciones del grupo. Queda registrada en la bitácora de la empresa.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>📋</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>presentar para decidir mejor</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Devolución</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>La respuesta honesta de otro empresario después de escuchar una presentación. No es un consejo ni una receta: es una perspectiva desde su propia gestión.</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>escuchar y devolver</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Línea Estratégica</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>El área de trabajo prioritaria que una empresa define para los próximos años. Ordena las decisiones y permite seguir los avances reunión a reunión.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>de la visión a la acción</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Brecha</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>La distancia entre dónde está hoy la empresa y dónde quiere estar. Identificarla es el paso previo a definir en qué trabajar.</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>📏</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>dónde estoy y dónde quiero estar</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Bitácora</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>El documento donde queda registrada cada reunión de la empresa en el grupo: fecha, tema y aportes. Es la memoria del proceso.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>📓</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>la memoria del proceso</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
-  </ignoredErrors>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/plantillas/Plantilla_Marco_Conceptual.xlsx
+++ b/plantillas/Plantilla_Marco_Conceptual.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +29,7 @@
     <font>
       <b val="1"/>
       <color rgb="001E2A2E"/>
-      <sz val="15"/>
+      <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
@@ -38,7 +38,7 @@
     <font>
       <b val="1"/>
       <color rgb="001E2A2E"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -54,11 +54,6 @@
       <i val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001E2A2E"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -96,20 +91,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -478,11 +474,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,10 +487,11 @@
           <t>Marco Conceptual del grupo</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="2" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -528,23 +525,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Escribí un concepto por fila en la pestaña CONCEPTOS. Vienen 6 ejemplos ya cargados: editalos, borrá los que no usen y agregá los suyos.</t>
+          <t>Escribí un concepto por fila en la pestaña CONCEPTOS. Vienen seis ejemplos ya cargados: editalos, borrá los que no usen y agregá los suyos.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="n"/>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Qué va en cada columna</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
+          <t>COLUMNA</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>QUÉ VA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
@@ -556,7 +558,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
@@ -568,55 +570,56 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>icono</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Opcional. Un emoji para la tarjeta. Si lo dejás vacío se usa 📌. Se copian de cualquier lado (🏛️ 📋 🔄 🎯 📊 🤝).</t>
+          <t>Opcional. Un emoji. Si lo dejás vacío se usa 📌.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>frase_corta</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Opcional. Una frase de tres o cuatro palabras que resume el concepto; aparece en gris chiquito abajo del título. Si no se te ocurre ninguna, dejala vacía: la tarjeta se ve igual de bien.</t>
+          <t>Opcional. Tres o cuatro palabras que resumen el concepto; se ven en gris abajo del título. Si no se te ocurre, dejala vacía.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>mostrar_en_web</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Escribí TRUE para que se vea, FALSE para esconderlo sin borrar la fila. Si lo dejás vacío, se muestra.</t>
+          <t>TRUE para que se vea, FALSE para esconderlo sin borrar la fila. Vacío = se muestra.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>orden</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Opcional. El número define en qué orden aparecen las tarjetas. Si está vacío, se usan en el orden de la planilla.</t>
+          <t>Opcional. Define en qué orden aparecen las tarjetas.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="n"/>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -627,18 +630,6 @@
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Subí este archivo a la carpeta del grupo en Drive, compartilo como Lector con la cuenta de servicio del sitio, y pegá su link en Configuración → Marco Conceptual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Ojo</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>No cambies los nombres de las columnas de la fila 3 de CONCEPTOS: el sitio las busca por ese nombre.</t>
         </is>
       </c>
     </row>
@@ -665,78 +656,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>CONCEPTOS — el vocabulario común del grupo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Un concepto por fila. Las 6 filas de abajo son ejemplos reales: editalos, borrá los que no correspondan y sumá los del grupo. Solo «titulo» y «descripcion» son obligatorios.</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Un concepto por fila. Los seis de abajo son ejemplos: editalos o borralos. Solo «titulo» y «descripcion» son obligatorios.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>icono</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>frase_corta</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>mostrar_en_web</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>orden</t>
         </is>
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Directorio Colaborativo</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Un espacio de dirección donde cada empresa presenta sus decisiones y recibe la mirada de otros empresarios. No es una consultoría: son pares que aportan desde su propia experiencia.</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>🏛️</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>entre pares, no consultores</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -771,32 +762,32 @@
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Devolución</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>La respuesta honesta de otro empresario después de escuchar una presentación. No es un consejo ni una receta: es una perspectiva desde su propia gestión.</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>🔄</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>escuchar y devolver</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -831,32 +822,32 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Brecha</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>La distancia entre dónde está hoy la empresa y dónde quiere estar. Identificarla es el paso previo a definir en qué trabajar.</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>📏</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>dónde estoy y dónde quiero estar</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -895,6 +886,11 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E4:E60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escribí TRUE o FALSE." promptTitle="TRUE o FALSE" prompt="TRUE = sí · FALSE = no · vacío = TRUE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>